--- a/data/final/tables/bootstrap_summary_treatment.xlsx
+++ b/data/final/tables/bootstrap_summary_treatment.xlsx
@@ -492,19 +492,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2173105.9151329</v>
+        <v>2172957.9761095</v>
       </c>
       <c r="E2" t="n">
-        <v>2172491.1705</v>
+        <v>2172639.756</v>
       </c>
       <c r="F2" t="n">
-        <v>2027142.9985</v>
+        <v>2027612.440225</v>
       </c>
       <c r="G2" t="n">
-        <v>2330312.874225</v>
+        <v>2321278.701975</v>
       </c>
       <c r="H2" t="n">
-        <v>76658.13864852587</v>
+        <v>75956.68918405191</v>
       </c>
       <c r="I2" t="n">
         <v>10000</v>
@@ -527,19 +527,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2410028.567033403</v>
+        <v>2408309.66777477</v>
       </c>
       <c r="E3" t="n">
-        <v>2406993.078328744</v>
+        <v>2405481.091074449</v>
       </c>
       <c r="F3" t="n">
-        <v>2207081.452086482</v>
+        <v>2201657.487343148</v>
       </c>
       <c r="G3" t="n">
-        <v>2628749.357104806</v>
+        <v>2625728.947864734</v>
       </c>
       <c r="H3" t="n">
-        <v>106564.803784021</v>
+        <v>107658.6344303894</v>
       </c>
       <c r="I3" t="n">
         <v>10000</v>
@@ -562,19 +562,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5819592615716.861</v>
+        <v>5811544678426.684</v>
       </c>
       <c r="E4" t="n">
-        <v>5793615679230.234</v>
+        <v>5786339279647.822</v>
       </c>
       <c r="F4" t="n">
-        <v>4871208546166.829</v>
+        <v>4847295692099.462</v>
       </c>
       <c r="G4" t="n">
-        <v>6910323187734.372</v>
+        <v>6894452507937.247</v>
       </c>
       <c r="H4" t="n">
-        <v>515361961336.395</v>
+        <v>519925591462.637</v>
       </c>
       <c r="I4" t="n">
         <v>10000</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>39.19902975165142</v>
+        <v>39.19819342238151</v>
       </c>
       <c r="E5" t="n">
-        <v>39.1992989983972</v>
+        <v>39.193</v>
       </c>
       <c r="F5" t="n">
-        <v>38.54108011022044</v>
+        <v>38.56156156156156</v>
       </c>
       <c r="G5" t="n">
-        <v>39.86288447766403</v>
+        <v>39.868</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3373482355480265</v>
+        <v>0.332288617281822</v>
       </c>
       <c r="I5" t="n">
         <v>10000</v>
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.50805661770766</v>
+        <v>10.51207232452869</v>
       </c>
       <c r="E6" t="n">
-        <v>10.47106318143617</v>
+        <v>10.46968368162325</v>
       </c>
       <c r="F6" t="n">
-        <v>9.540976173976034</v>
+        <v>9.516652190884257</v>
       </c>
       <c r="G6" t="n">
-        <v>11.70614729285794</v>
+        <v>11.69392999723415</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5591076071445559</v>
+        <v>0.5651262133053296</v>
       </c>
       <c r="I6" t="n">
         <v>10000</v>
@@ -667,19 +667,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>110.731823937185</v>
+        <v>110.8230002563231</v>
       </c>
       <c r="E7" t="n">
-        <v>109.6431641501221</v>
+        <v>109.6142764859273</v>
       </c>
       <c r="F7" t="n">
-        <v>91.03022636747993</v>
+        <v>90.56666892343246</v>
       </c>
       <c r="G7" t="n">
-        <v>137.0338844453672</v>
+        <v>136.7479987985982</v>
       </c>
       <c r="H7" t="n">
-        <v>11.8756750673703</v>
+        <v>12.01034519929541</v>
       </c>
       <c r="I7" t="n">
         <v>10000</v>
@@ -702,19 +702,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.389554116666667</v>
+        <v>2.388868896666667</v>
       </c>
       <c r="E8" t="n">
-        <v>2.386566666666667</v>
+        <v>2.385833333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>2.228899166666666</v>
+        <v>2.22993125</v>
       </c>
       <c r="G8" t="n">
-        <v>2.569304166666667</v>
+        <v>2.566135</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08626688114075676</v>
+        <v>0.08564661984144509</v>
       </c>
       <c r="I8" t="n">
         <v>10000</v>
@@ -737,19 +737,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.702228269377003</v>
+        <v>2.696975926000794</v>
       </c>
       <c r="E9" t="n">
-        <v>2.702228340731376</v>
+        <v>2.700461288008436</v>
       </c>
       <c r="F9" t="n">
-        <v>1.993490338439898</v>
+        <v>1.979985505820838</v>
       </c>
       <c r="G9" t="n">
-        <v>3.418931739663488</v>
+        <v>3.414638369663904</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3652742980958475</v>
+        <v>0.3653634850354426</v>
       </c>
       <c r="I9" t="n">
         <v>10000</v>
@@ -772,19 +772,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.435449590138361</v>
+        <v>7.407156272577467</v>
       </c>
       <c r="E10" t="n">
-        <v>7.302038007312868</v>
+        <v>7.292491168390614</v>
       </c>
       <c r="F10" t="n">
-        <v>3.974003730167668</v>
+        <v>3.920342620175732</v>
       </c>
       <c r="G10" t="n">
-        <v>11.68909424158186</v>
+        <v>11.6597551981982</v>
       </c>
       <c r="H10" t="n">
-        <v>1.988238272374096</v>
+        <v>1.976442371608622</v>
       </c>
       <c r="I10" t="n">
         <v>10000</v>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5838205999999999</v>
+        <v>0.583871</v>
       </c>
       <c r="E11" t="n">
         <v>0.584</v>
@@ -816,10 +816,10 @@
         <v>0.554</v>
       </c>
       <c r="G11" t="n">
-        <v>0.614</v>
+        <v>0.615</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01549041028898499</v>
+        <v>0.01557587942306887</v>
       </c>
       <c r="I11" t="n">
         <v>10000</v>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.4151937</v>
+        <v>0.4151304</v>
       </c>
       <c r="E12" t="n">
         <v>0.415</v>
       </c>
       <c r="F12" t="n">
-        <v>0.385</v>
+        <v>0.384</v>
       </c>
       <c r="G12" t="n">
         <v>0.445</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01548386758292425</v>
+        <v>0.01558756212655798</v>
       </c>
       <c r="I12" t="n">
         <v>10000</v>
@@ -873,11 +873,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>proportion_otros</t>
+          <t>proportion_others</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.001577877381142992</v>
+        <v>0.001584073604060956</v>
       </c>
       <c r="E13" t="n">
         <v>0.001000000000000112</v>
@@ -889,7 +889,7 @@
         <v>0.004000000000000004</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0008097886820559704</v>
+        <v>0.0008139121311896801</v>
       </c>
       <c r="I13" t="n">
         <v>10000</v>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.7049666999999999</v>
+        <v>0.7049733</v>
       </c>
       <c r="E14" t="n">
         <v>0.705</v>
@@ -921,10 +921,10 @@
         <v>0.677</v>
       </c>
       <c r="G14" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01434236945090128</v>
+        <v>0.01450167635039815</v>
       </c>
       <c r="I14" t="n">
         <v>10000</v>
@@ -943,23 +943,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>proportion_otros</t>
+          <t>proportion_others</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.2950333000000001</v>
+        <v>0.2950267000000001</v>
       </c>
       <c r="E15" t="n">
         <v>0.295</v>
       </c>
       <c r="F15" t="n">
-        <v>0.267</v>
+        <v>0.266</v>
       </c>
       <c r="G15" t="n">
         <v>0.323</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01434236945090128</v>
+        <v>0.01450167635039815</v>
       </c>
       <c r="I15" t="n">
         <v>10000</v>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.6163351999999999</v>
+        <v>0.6160258000000001</v>
       </c>
       <c r="E16" t="n">
         <v>0.616</v>
@@ -994,7 +994,7 @@
         <v>0.646</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01532590386544721</v>
+        <v>0.01536847270731012</v>
       </c>
       <c r="I16" t="n">
         <v>10000</v>
@@ -1013,11 +1013,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>proportion_otros</t>
+          <t>proportion_others</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.3836648</v>
+        <v>0.3839742</v>
       </c>
       <c r="E17" t="n">
         <v>0.384</v>
@@ -1029,7 +1029,7 @@
         <v>0.414</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01532590386544721</v>
+        <v>0.01536847270731012</v>
       </c>
       <c r="I17" t="n">
         <v>10000</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.1721087</v>
+        <v>0.1717572</v>
       </c>
       <c r="E18" t="n">
         <v>0.172</v>
@@ -1064,7 +1064,7 @@
         <v>0.196</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01199496028410356</v>
+        <v>0.01196648519143293</v>
       </c>
       <c r="I18" t="n">
         <v>10000</v>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.3771400585221111</v>
+        <v>0.3768352062951179</v>
       </c>
       <c r="E19" t="n">
         <v>0.3773804446443933</v>
@@ -1099,7 +1099,7 @@
         <v>0.3969685126052191</v>
       </c>
       <c r="H19" t="n">
-        <v>0.01043157896593772</v>
+        <v>0.01042688680828625</v>
       </c>
       <c r="I19" t="n">
         <v>10000</v>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.1423434307</v>
+        <v>0.1421134818</v>
       </c>
       <c r="E20" t="n">
         <v>0.142416</v>
@@ -1134,7 +1134,7 @@
         <v>0.157584</v>
       </c>
       <c r="H20" t="n">
-        <v>0.007857164022536708</v>
+        <v>0.007847160519633255</v>
       </c>
       <c r="I20" t="n">
         <v>10000</v>
@@ -1157,19 +1157,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.5539386000000002</v>
+        <v>0.5542855000000001</v>
       </c>
       <c r="E21" t="n">
         <v>0.554</v>
       </c>
       <c r="F21" t="n">
-        <v>0.523</v>
+        <v>0.524</v>
       </c>
       <c r="G21" t="n">
         <v>0.585</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01572008085647821</v>
+        <v>0.01563790408444861</v>
       </c>
       <c r="I21" t="n">
         <v>10000</v>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.4968304561431652</v>
+        <v>0.4967952701770189</v>
       </c>
       <c r="E22" t="n">
         <v>0.4970754469896899</v>
@@ -1201,10 +1201,10 @@
         <v>0.4927220311697053</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4994707198625361</v>
+        <v>0.4994236678412428</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00174050323456056</v>
+        <v>0.001739175728907297</v>
       </c>
       <c r="I22" t="n">
         <v>10000</v>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.2468435312</v>
+        <v>0.2468085649</v>
       </c>
       <c r="E23" t="n">
         <v>0.247084</v>
@@ -1236,10 +1236,10 @@
         <v>0.242775</v>
       </c>
       <c r="G23" t="n">
-        <v>0.249471</v>
+        <v>0.249424</v>
       </c>
       <c r="H23" t="n">
-        <v>0.001726887380065328</v>
+        <v>0.001725587183859711</v>
       </c>
       <c r="I23" t="n">
         <v>10000</v>
